--- a/Paper2_Package/03_RESULTS/Task8_final_ranking/task8_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task8_final_ranking/task8_supporting.xlsx
@@ -595,17 +595,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RET</t>
+          <t>RRM1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6593745617725424</v>
+        <v>0.6576216519422241</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9781236853176272</v>
+        <v>0.9728649558266724</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -614,17 +614,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RRM1</t>
+          <t>HSP90AB1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6576216519422241</v>
+        <v>0.6567101388304585</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9728649558266724</v>
+        <v>0.9701304164913755</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -633,17 +633,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HSP90AB1</t>
+          <t>ODC1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6567101388304585</v>
+        <v>0.6471743093535267</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9701304164913755</v>
+        <v>0.9415229280605806</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -652,17 +652,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ODC1</t>
+          <t>CDK1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6471743093535267</v>
+        <v>0.644229420838592</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9415229280605806</v>
+        <v>0.9326882625157762</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -671,17 +671,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDK1</t>
+          <t>STS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.644229420838592</v>
+        <v>0.6317487028467255</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9326882625157762</v>
+        <v>0.8952461085401767</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -690,17 +690,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STS</t>
+          <t>TOP1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6317487028467255</v>
+        <v>0.6316084700603</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8952461085401767</v>
+        <v>0.8948254101809003</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -709,17 +709,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TOP1</t>
+          <t>CYP3A7</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6316084700603</v>
+        <v>0.6256485766372177</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8948254101809003</v>
+        <v>0.8769457299116533</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -728,17 +728,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CYP3A7</t>
+          <t>XPO1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6256485766372177</v>
+        <v>0.6230542700883466</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8769457299116533</v>
+        <v>0.8691628102650399</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -747,17 +747,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XPO1</t>
+          <t>ERBB2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6230542700883466</v>
+        <v>0.6064366848969288</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8691628102650399</v>
+        <v>0.8193100546907867</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -766,17 +766,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CPT2</t>
+          <t>HSP90AA1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6076286635815453</v>
+        <v>0.5923432898611695</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8228859907446361</v>
+        <v>0.7770298695835086</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -785,17 +785,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ERBB2</t>
+          <t>GSR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6064366848969288</v>
+        <v>0.5800729210489411</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8193100546907867</v>
+        <v>0.7402187631468238</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -804,17 +804,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NR3C1</t>
+          <t>CASP7</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5971112045996354</v>
+        <v>0.5707474407516476</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7913336137989062</v>
+        <v>0.7122423222549432</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -823,17 +823,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SLC22A11</t>
+          <t>PSMB2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5933249193661477</v>
+        <v>0.5649978965082035</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7799747580984434</v>
+        <v>0.6949936895246108</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -842,17 +842,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSP90AA1</t>
+          <t>EZH2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5923432898611695</v>
+        <v>0.5621231243864815</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7770298695835086</v>
+        <v>0.6863693731594447</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -861,17 +861,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GSR</t>
+          <t>IDH2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5800729210489411</v>
+        <v>0.5430514654326181</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7402187631468238</v>
+        <v>0.6291543962978544</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -880,17 +880,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CASP7</t>
+          <t>PSMB8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5707474407516476</v>
+        <v>0.5310615621932407</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7122423222549432</v>
+        <v>0.5931846865797223</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -899,17 +899,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PSMB2</t>
+          <t>HDAC2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5649978965082035</v>
+        <v>0.5286776048240078</v>
       </c>
       <c r="C18" t="n">
         <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6949936895246108</v>
+        <v>0.5860328144720236</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -918,17 +918,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EZH2</t>
+          <t>PLA2G2A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5621231243864815</v>
+        <v>0.5231384097602019</v>
       </c>
       <c r="C19" t="n">
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6863693731594447</v>
+        <v>0.5694152292806058</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -937,17 +937,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RAMP1</t>
+          <t>PSMB9</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5553218342448464</v>
+        <v>0.5152853737203759</v>
       </c>
       <c r="C20" t="n">
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6659655027345394</v>
+        <v>0.5458561211611275</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -956,17 +956,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IDH2</t>
+          <t>CHRM2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5430514654326181</v>
+        <v>0.504978263918104</v>
       </c>
       <c r="C21" t="n">
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6291543962978544</v>
+        <v>0.5149347917543121</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -975,17 +975,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PSMB8</t>
+          <t>CASP3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5310615621932407</v>
+        <v>0.502874772121722</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5931846865797223</v>
+        <v>0.5086243163651661</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -994,77 +994,77 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HDAC2</t>
+          <t>KCNJ5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5286776048240078</v>
+        <v>0.4988781377085962</v>
       </c>
       <c r="C23" t="n">
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5860328144720236</v>
+        <v>0.9966344131257888</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KIF11</t>
+          <t>EPRS1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5279063244986677</v>
+        <v>0.4985976721357453</v>
       </c>
       <c r="C24" t="n">
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5837189734960033</v>
+        <v>0.9957930164072361</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLA2G2A</t>
+          <t>TUBA1B</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5231384097602019</v>
+        <v>0.4980367409900433</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5694152292806058</v>
+        <v>0.9941102229701304</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PSMB9</t>
+          <t>ATP6V1H</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5152853737203759</v>
+        <v>0.4977562754171924</v>
       </c>
       <c r="C26" t="n">
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5458561211611275</v>
+        <v>0.9932688262515776</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/Paper2_Package/03_RESULTS/Task8_final_ranking/task8_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task8_final_ranking/task8_supporting.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="evidence_verdict_counts" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="inflammation_only_targets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="candidates_under_alternative_ti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1070,4 +1071,851 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Drug</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>best_target</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_targets</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>coherence</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>specificity_lower95</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mechanism_consistent_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ERDAFITINIB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LENVATINIB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FOSTAMATINIB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>82</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AMLODIPINE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PONATINIB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EFONIDIPINE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DROTAVERINE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>REGORAFENIB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NINTEDANIB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>38</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PAZOPANIB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NILVADIPINE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RIPRETINIB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MIDOSTAURIN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AMUVATINIB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MIBEFRADIL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TRIMEBUTINE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MANIDIPINE 6300</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>48</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ISRADIPINE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>49</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NITRENDIPINE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AMIODARONE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>51</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SPIRONOLACTONE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>26</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NIFEDIPINE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NIMODIPINE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BENIDIPINE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LEVOMENTHOL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>39</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FELODIPINE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>37</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NISOLDIPINE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IMATINIB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SUNITINIB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PDGFRA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>43</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MICONAZOLE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CACNA1C</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Paper2_Package/03_RESULTS/Task8_final_ranking/task8_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task8_final_ranking/task8_supporting.xlsx
@@ -596,17 +596,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RRM1</t>
+          <t>RET</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6576216519422241</v>
+        <v>0.6593745617725424</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9728649558266724</v>
+        <v>0.9781236853176272</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -615,17 +615,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HSP90AB1</t>
+          <t>RRM1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6567101388304585</v>
+        <v>0.6576216519422241</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9701304164913755</v>
+        <v>0.9728649558266724</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -634,17 +634,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ODC1</t>
+          <t>HSP90AB1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6471743093535267</v>
+        <v>0.6567101388304585</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9415229280605806</v>
+        <v>0.9701304164913755</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -653,17 +653,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDK1</t>
+          <t>ODC1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.644229420838592</v>
+        <v>0.6471743093535267</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9326882625157762</v>
+        <v>0.9415229280605806</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -672,17 +672,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STS</t>
+          <t>CDK1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6317487028467255</v>
+        <v>0.644229420838592</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8952461085401767</v>
+        <v>0.9326882625157762</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -691,17 +691,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TOP1</t>
+          <t>STS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6316084700603</v>
+        <v>0.6317487028467255</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8948254101809003</v>
+        <v>0.8952461085401767</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -710,17 +710,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CYP3A7</t>
+          <t>TOP1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6256485766372177</v>
+        <v>0.6316084700603</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8769457299116533</v>
+        <v>0.8948254101809003</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -729,17 +729,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XPO1</t>
+          <t>CYP3A7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6230542700883466</v>
+        <v>0.6256485766372177</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8691628102650399</v>
+        <v>0.8769457299116533</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ERBB2</t>
+          <t>XPO1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6064366848969288</v>
+        <v>0.6230542700883466</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8193100546907867</v>
+        <v>0.8691628102650399</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -767,17 +767,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSP90AA1</t>
+          <t>CPT2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5923432898611695</v>
+        <v>0.6076286635815453</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7770298695835086</v>
+        <v>0.8228859907446361</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -786,17 +786,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GSR</t>
+          <t>ERBB2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5800729210489411</v>
+        <v>0.6064366848969288</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7402187631468238</v>
+        <v>0.8193100546907867</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -805,17 +805,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CASP7</t>
+          <t>NR3C1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5707474407516476</v>
+        <v>0.5971112045996354</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7122423222549432</v>
+        <v>0.7913336137989062</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -824,17 +824,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PSMB2</t>
+          <t>SLC22A11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5649978965082035</v>
+        <v>0.5933249193661477</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6949936895246108</v>
+        <v>0.7799747580984434</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -843,17 +843,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EZH2</t>
+          <t>HSP90AA1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5621231243864815</v>
+        <v>0.5923432898611695</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6863693731594447</v>
+        <v>0.7770298695835086</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -862,17 +862,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IDH2</t>
+          <t>GSR</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5430514654326181</v>
+        <v>0.5800729210489411</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6291543962978544</v>
+        <v>0.7402187631468238</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -881,17 +881,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PSMB8</t>
+          <t>CASP7</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5310615621932407</v>
+        <v>0.5707474407516476</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5931846865797223</v>
+        <v>0.7122423222549432</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -900,17 +900,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HDAC2</t>
+          <t>PSMB2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5286776048240078</v>
+        <v>0.5649978965082035</v>
       </c>
       <c r="C18" t="n">
         <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5860328144720236</v>
+        <v>0.6949936895246108</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -919,17 +919,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PLA2G2A</t>
+          <t>EZH2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5231384097602019</v>
+        <v>0.5621231243864815</v>
       </c>
       <c r="C19" t="n">
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5694152292806058</v>
+        <v>0.6863693731594447</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -938,17 +938,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PSMB9</t>
+          <t>RAMP1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5152853737203759</v>
+        <v>0.5553218342448464</v>
       </c>
       <c r="C20" t="n">
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5458561211611275</v>
+        <v>0.6659655027345394</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -957,17 +957,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHRM2</t>
+          <t>IDH2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.504978263918104</v>
+        <v>0.5430514654326181</v>
       </c>
       <c r="C21" t="n">
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5149347917543121</v>
+        <v>0.6291543962978544</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -976,17 +976,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CASP3</t>
+          <t>PSMB8</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.502874772121722</v>
+        <v>0.5310615621932407</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5086243163651661</v>
+        <v>0.5931846865797223</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -995,77 +995,77 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KCNJ5</t>
+          <t>HDAC2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4988781377085962</v>
+        <v>0.5286776048240078</v>
       </c>
       <c r="C23" t="n">
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9966344131257888</v>
+        <v>0.5860328144720236</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EPRS1</t>
+          <t>KIF11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4985976721357453</v>
+        <v>0.5279063244986677</v>
       </c>
       <c r="C24" t="n">
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9957930164072361</v>
+        <v>0.5837189734960033</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TUBA1B</t>
+          <t>PLA2G2A</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4980367409900433</v>
+        <v>0.5231384097602019</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9941102229701304</v>
+        <v>0.5694152292806058</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ATP6V1H</t>
+          <t>PSMB9</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4977562754171924</v>
+        <v>0.5152853737203759</v>
       </c>
       <c r="C26" t="n">
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9932688262515776</v>
+        <v>0.5458561211611275</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
